--- a/artfynd/A 35594-2026 artfynd.xlsx
+++ b/artfynd/A 35594-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136194051</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35594-2026 artfynd.xlsx
+++ b/artfynd/A 35594-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136194051</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35594-2026 artfynd.xlsx
+++ b/artfynd/A 35594-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136194051</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>136194050</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>136194052</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>136194053</v>
       </c>
       <c r="B8" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35594-2026 artfynd.xlsx
+++ b/artfynd/A 35594-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136194051</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
